--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104540_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104540_W10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7709</v>
+        <v>3.5286</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7374</v>
+        <v>1.6191</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0335</v>
+        <v>1.9095</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3542</v>
+        <v>1.7483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4906</v>
+        <v>0.02</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8637</v>
+        <v>1.7282</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4435</v>
+        <v>1.6173</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3401</v>
+        <v>0.3512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7837</v>
+        <v>1.2661</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9107</v>
+        <v>0.131</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8307</v>
+        <v>-0.3312</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08</v>
+        <v>0.4622</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1633</v>
+        <v>0.5331</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0819</v>
+        <v>-0.1072</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0813</v>
+        <v>0.6404</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7071</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3767</v>
+        <v>3.31</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3404</v>
+        <v>2.1907</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0363</v>
+        <v>1.1193</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7407</v>
+        <v>-0.393</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0187</v>
+        <v>1.7987</v>
       </c>
       <c r="I3" t="n">
-        <v>1.722</v>
+        <v>-2.1917</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6355</v>
+        <v>-1.1561</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3668</v>
+        <v>0.9675</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2688</v>
+        <v>-2.1236</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1052</v>
+        <v>0.763</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.348</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4532</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3826</v>
+        <v>-0.4272</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4143</v>
+        <v>-0.0307</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7969000000000001</v>
+        <v>-0.3965</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>4.3579</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>4.5157</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0264</v>
+        <v>3.1755</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3605</v>
+        <v>1.5315</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6659</v>
+        <v>1.6441</v>
       </c>
       <c r="G4" t="n">
-        <v>1.053</v>
+        <v>1.0778</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8172</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4009</v>
+        <v>0.3845</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5266</v>
+        <v>-0.5311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6521</v>
+        <v>0.6933</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3184</v>
+        <v>1.3482</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0266</v>
+        <v>0.0977</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1331</v>
+        <v>0.0575</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1064</v>
+        <v>0.0402</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5038</v>
+        <v>2.3249</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6151</v>
+        <v>2.5312</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8888</v>
+        <v>-0.2063</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3679</v>
+        <v>1.3656</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8126</v>
+        <v>0.4938</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1805</v>
+        <v>0.8718</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0896</v>
+        <v>0.4158</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0137</v>
+        <v>-0.3662</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1033</v>
+        <v>0.782</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7217</v>
+        <v>0.9498</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>0.0898</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2721</v>
+        <v>0.712</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6926</v>
+        <v>0.9169</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5795</v>
+        <v>-0.2048</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3707</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>4.5314</v>
+        <v>2.3367</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. LOPEZ DE LA TORRE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1781</v>
+        <v>0.3016</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.1575</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1781</v>
+        <v>0.1442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1573</v>
+        <v>0.5759</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.5656</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1573</v>
+        <v>0.0103</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.4597</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.8101</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.3505</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1573</v>
+        <v>0.1162</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.2446</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0209</v>
+        <v>-0.0953</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.3022</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0209</v>
+        <v>0.2069</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>R. LOPEZ DE LA TORRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3246</v>
+        <v>0.2102</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1353</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1893</v>
+        <v>0.2102</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5745</v>
+        <v>0.1579</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5612</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0133</v>
+        <v>0.1579</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4726</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8139</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3413</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1019</v>
+        <v>0.1579</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2526</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3546</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7138</v>
+        <v>0.0523</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6079</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1059</v>
+        <v>0.0523</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6354</v>
+        <v>-0.1972</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0304</v>
+        <v>-1.5798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.395</v>
+        <v>1.3827</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9847</v>
+        <v>-0.0137</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.062</v>
+        <v>-2.9554</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07729999999999999</v>
+        <v>2.9417</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9293</v>
+        <v>-1.4794</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9666</v>
+        <v>-3.9589</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>2.4795</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0554</v>
+        <v>1.4657</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0954</v>
+        <v>1.0035</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>0.4622</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0278</v>
+        <v>-0.5492</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3811</v>
+        <v>-0.1004</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4089</v>
+        <v>-0.4488</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3214</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0863</v>
+        <v>-0.6301</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9596</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1267</v>
+        <v>0.3533</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0145</v>
+        <v>-0.9805</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1428</v>
+        <v>-1.0626</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1573</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.769</v>
+        <v>-0.9388</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>-0.976</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7864</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7546</v>
+        <v>-0.0417</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1255</v>
+        <v>-0.0866</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>0.0449</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0209</v>
+        <v>0.0349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1905</v>
+        <v>-0.3115</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2114</v>
+        <v>0.3463</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1837</v>
+        <v>-1.0488</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1362</v>
+        <v>-0.963</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9525</v>
+        <v>-0.0858</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2966</v>
+        <v>-0.0116</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4614</v>
+        <v>0.1463</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1648</v>
+        <v>-0.1579</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0183</v>
+        <v>-0.7724</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6927</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6744</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2784</v>
+        <v>0.7608</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7688</v>
+        <v>0.129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4904</v>
+        <v>0.6317</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4122</v>
+        <v>0.0523</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8861</v>
+        <v>-0.1906</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4739</v>
+        <v>0.2429</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2605</v>
+        <v>-1.2073</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.196</v>
+        <v>-2.6576</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9355</v>
+        <v>1.4503</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0086</v>
+        <v>0.3149</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9566</v>
+        <v>1.4782</v>
       </c>
       <c r="I11" t="n">
-        <v>2.948</v>
+        <v>-1.1633</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4339</v>
+        <v>0.0115</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.9287</v>
+        <v>0.6895</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4948</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4253</v>
+        <v>0.3033</v>
       </c>
       <c r="N11" t="n">
-        <v>0.972</v>
+        <v>0.7887</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4532</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6129</v>
+        <v>-0.4539</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7621</v>
+        <v>-0.3929</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8508</v>
+        <v>-0.0611</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3005</v>
+        <v>-1.2402</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5372</v>
+        <v>-1.5435</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2368</v>
+        <v>0.3033</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5872</v>
+        <v>-1.5909</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4154</v>
+        <v>-1.4214</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0599</v>
+        <v>0.1231</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0181</v>
+        <v>0.0185</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2201</v>
+        <v>-2.9793</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5255</v>
+        <v>-3.3669</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3054</v>
+        <v>0.3876</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5315</v>
+        <v>-1.5393</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.618</v>
+        <v>-1.6255</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7884</v>
+        <v>-0.8094</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7431</v>
+        <v>-0.73</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1669</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4688</v>
+        <v>-0.2812</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3018</v>
+        <v>0.3648</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.844800000000001</v>
+        <v>5.547899999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.466800000000001</v>
+        <v>-3.064199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>8.311800000000002</v>
+        <v>8.612400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6819</v>
+        <v>0.7114000000000003</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1754</v>
+        <v>1.2184</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4931999999999996</v>
+        <v>-0.5070999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.5948</v>
+        <v>-3.8293</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.5011</v>
+        <v>-2.6487</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.0936</v>
+        <v>-1.1806</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2769</v>
+        <v>4.5404</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6766</v>
+        <v>3.8667</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6004</v>
+        <v>0.6735999999999998</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>9.0732</v>
+        <v>9.105200000000002</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5290999999999997</v>
+        <v>0.1633999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4365</v>
+        <v>-0.7238</v>
       </c>
       <c r="U14" t="n">
-        <v>0.907</v>
+        <v>0.8872</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6922</v>
+        <v>4.6733</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6377</v>
+        <v>10.5941</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.945500000000001</v>
+        <v>-5.9208</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6932</v>
+        <v>4.9406</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3412</v>
+        <v>4.4426</v>
       </c>
       <c r="F15" t="n">
-        <v>0.352</v>
+        <v>0.498</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4423</v>
+        <v>5.44</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5209</v>
+        <v>2.5189</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9214</v>
+        <v>2.9211</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8099</v>
+        <v>4.7936</v>
       </c>
       <c r="K15" t="n">
-        <v>2.459</v>
+        <v>2.4476</v>
       </c>
       <c r="L15" t="n">
-        <v>2.351</v>
+        <v>2.3459</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6324</v>
+        <v>0.6465</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1101</v>
+        <v>0.1348</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3587</v>
+        <v>0.4857</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7756</v>
+        <v>1.4864</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3951</v>
+        <v>-1.1641</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1707</v>
+        <v>2.6505</v>
       </c>
       <c r="G16" t="n">
-        <v>0.108</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2622</v>
+        <v>-1.2881</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3701</v>
+        <v>1.3751</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2932</v>
+        <v>-0.3482</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8578</v>
+        <v>-1.9045</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4011</v>
+        <v>0.4352</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5956</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4823</v>
+        <v>1.2204</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0737</v>
+        <v>0.3709</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4086</v>
+        <v>0.8495</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3285</v>
+        <v>0.7109</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7542</v>
+        <v>-0.2831</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0828</v>
+        <v>0.994</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8015</v>
+        <v>-0.7794</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.517</v>
+        <v>-0.506</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4639</v>
+        <v>-0.4683</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6132</v>
+        <v>-0.6173</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3375</v>
+        <v>-0.3111</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5441</v>
+        <v>0.8953</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2903</v>
+        <v>0.1852</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8344</v>
+        <v>0.7101</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.148</v>
+        <v>0.3767</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8888</v>
+        <v>-1.0227</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0368</v>
+        <v>1.3993</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6019</v>
+        <v>-0.5886</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0561</v>
+        <v>1.0678</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6579</v>
+        <v>-1.6564</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.403</v>
+        <v>-1.4238</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8068</v>
+        <v>0.7961</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8011</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2493</v>
+        <v>0.2716</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.803</v>
+        <v>1.0045</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5142</v>
+        <v>0.4012</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2888</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.4161</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7628</v>
+        <v>-1.1201</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6952</v>
+        <v>0.7039</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9838</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4747</v>
+        <v>0.4794</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5091</v>
+        <v>0.511</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9187</v>
       </c>
       <c r="N19" t="n">
-        <v>0.44</v>
+        <v>0.4449</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4023</v>
+        <v>0.0487</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>-0.0536</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1028</v>
+        <v>0.1024</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7311</v>
+        <v>-0.7859</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3601</v>
+        <v>-0.1258</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0912</v>
+        <v>-0.6601</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6567</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3262</v>
+        <v>0.3219</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3306</v>
+        <v>0.3338</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1816</v>
+        <v>0.1672</v>
       </c>
       <c r="K20" t="n">
-        <v>0.107</v>
+        <v>0.0927</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4751</v>
+        <v>0.4886</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1171</v>
+        <v>0.0545</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1785</v>
+        <v>-0.2929</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0614</v>
+        <v>0.3474</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2656</v>
+        <v>-1.3384</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.284</v>
+        <v>-2.1812</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0184</v>
+        <v>0.8428</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6333</v>
+        <v>-1.0771</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2197</v>
+        <v>-0.8358</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.853</v>
+        <v>-0.2414</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3017</v>
+        <v>-2.5293</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7886</v>
+        <v>-1.352</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0903</v>
+        <v>-1.1773</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3316</v>
+        <v>1.4522</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5689</v>
+        <v>0.5162</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2373</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1391</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0061</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1452</v>
+        <v>0.8168</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3214</v>
+        <v>-1.2472</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4141</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3914</v>
+        <v>-1.5928</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5045</v>
+        <v>-2.1232</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1131</v>
+        <v>0.5304</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0754</v>
+        <v>-0.6586</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8355</v>
+        <v>0.1966</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2399</v>
+        <v>-0.8551</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5023</v>
+        <v>-0.3594</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3374</v>
+        <v>0.7435</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1649</v>
+        <v>-1.1029</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4269</v>
+        <v>-0.2992</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5019</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.925</v>
+        <v>0.2477</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9699</v>
+        <v>0.5713</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0948</v>
+        <v>0.2457</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1249</v>
+        <v>0.3256</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2534</v>
+        <v>0.3155</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.405</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.16</v>
+        <v>-2.1029</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6274</v>
+        <v>-2.2231</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5326</v>
+        <v>0.1202</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6574</v>
+        <v>-3.0982</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1771</v>
+        <v>-1.2094</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5197000000000001</v>
+        <v>-1.8888</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4612</v>
+        <v>-2.929</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.6472</v>
+        <v>-1.4242</v>
       </c>
       <c r="L23" t="n">
-        <v>1.186</v>
+        <v>-1.5048</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1962</v>
+        <v>-0.1692</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4701</v>
+        <v>0.2148</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6663</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0755</v>
+        <v>0.54</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1512</v>
+        <v>-0.3836</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9243</v>
+        <v>0.9236</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1745</v>
+        <v>-2.181</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7961</v>
+        <v>-2.8115</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3784</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1034</v>
+        <v>-1.6825</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2136</v>
+        <v>-2.1961</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8899</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9149</v>
+        <v>-1.5148</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4169</v>
+        <v>-2.6834</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4981</v>
+        <v>1.1686</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1885</v>
+        <v>-0.1676</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2033</v>
+        <v>0.4873</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3918</v>
+        <v>-0.6549</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.0629</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9739</v>
+        <v>-0.2676</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4491</v>
+        <v>0.2047</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.844900000000001</v>
+        <v>-0.9025000000000007</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.311600000000002</v>
+        <v>-8.612200000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>3.466800000000001</v>
+        <v>7.709499999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6820999999999997</v>
+        <v>-0.7112999999999992</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1752</v>
+        <v>-1.2182</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4931999999999999</v>
+        <v>0.5068999999999998</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2767</v>
+        <v>-4.5403</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.6765</v>
+        <v>-3.867</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6003000000000007</v>
+        <v>-0.6736000000000004</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5946</v>
+        <v>3.8293</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5012</v>
+        <v>2.6486</v>
       </c>
       <c r="O25" t="n">
-        <v>1.0935</v>
+        <v>1.1807</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R25" t="n">
-        <v>9.0733</v>
+        <v>9.1053</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5295000000000002</v>
+        <v>4.482</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9070999999999999</v>
+        <v>-0.8870999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4364</v>
+        <v>5.3691</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.692</v>
+        <v>-4.6733</v>
       </c>
       <c r="W25" t="n">
-        <v>5.9456</v>
+        <v>5.9207</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.6376</v>
+        <v>-10.594</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104540_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104540_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.9208</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104540_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-10.594</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
